--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,17 +1624,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
+          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
+          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
+          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
+          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -1273,44 +1273,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,10 +1850,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Managing risk</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,17 +1624,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,17 +1624,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,17 +1624,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>VP, Portfolio Risk ManagerVP, Portfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-VP%2C-Portfolio-Risk-Manager-018983/1441140500/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
+          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
+          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
+          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
+          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -1295,39 +1295,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,10 +1877,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,17 +1624,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,12 +1700,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,22 +1862,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,12 +1538,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,22 +1862,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VP, Portfolio Risk ManagerVP, Portfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, FX Quantitative ResearchVice President, FX Quantitative ResearchGlobal MarketsSingapore, SG, 018983Global Markets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-VP%2C-Portfolio-Risk-Manager-018983/1441140500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Vice-President%2C-FX-Quantitative-Research-018983/1444398400/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>VP, Portfolio Risk ManagerVP, Portfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-VP%2C-Portfolio-Risk-Manager-018983/1441140500/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
+          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
+          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
+          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
+          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -1322,49 +1322,49 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,22 +1862,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1889,12 +1889,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1904,10 +1904,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vice President, FX Quantitative ResearchVice President, FX Quantitative ResearchGlobal MarketsSingapore, SG, 018983Global Markets</t>
+          <t>HR Compensation &amp; AnalyticsHR Compensation &amp; AnalyticsHuman ResourcesSingapore, SG, 018983Human Resources</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Vice-President%2C-FX-Quantitative-Research-018983/1444398400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-018983/1424289900/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VP, Portfolio Risk ManagerVP, Portfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Chief Information OfficeSingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-VP%2C-Portfolio-Risk-Manager-018983/1441140500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1444391100/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, FX Quantitative ResearchVice President, FX Quantitative ResearchGlobal MarketsSingapore, SG, 018983Global Markets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Vice-President%2C-FX-Quantitative-Research-018983/1444398400/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
+          <t>VP, Portfolio Risk ManagerVP, Portfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-VP%2C-Portfolio-Risk-Manager-018983/1441140500/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
+          <t>Associate, Credit Risk Infrastructure OfficerAssociate, Credit Risk Infrastructure OfficerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Infrastructure-Officer-018983/1431834600/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
+          <t>Associate, Credit Risk Exposure ManagementAssociate, Credit Risk Exposure ManagementRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Credit-Risk-Exposure-Management-HK/1427862000/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
+          <t>Model Quantitative Specialist AuditorModel Quantitative Specialist AuditorInternal AuditSingapore, SG, 018983Internal Audit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Model-Quantitative-Specialist-Auditor-018983/1427329300/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>HR Compensation &amp; Analytics AssociateHR Compensation &amp; Analytics AssociateHuman ResourcesSingapore, SG, 018983Human Resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-HR-Compensation-&amp;-Analytics-Associate-018983/1424289900/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>VP, Hedge Fund Credit Risk AnalystVP, Hedge Fund Credit Risk AnalystRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Hedge-Fund-Credit-Risk-Analyst-HK/1423355700/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>VP, Quantitative StrategistVP, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-VP%2C-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>VP, Operational Risk ManagerVP, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Operational Risk ManagerAssociate, Operational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-GM-Front-Office-Risk-Manager-HK/1412265600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing AnalystAssociate, Stress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Risk HQ AnalystAssociate, Risk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>GM Front Office Risk ManagerGM Front Office Risk ManagerGlobal MarketsSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-GM-Front-Office-Risk-Manager-018983/1410432400/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -1354,49 +1354,49 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1916,12 +1916,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1931,10 +1931,64 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Singapore, SG, 018983</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Risk and Regulation</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
+          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,12 +1484,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1592,22 +1592,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,22 +1808,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,22 +1862,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1889,22 +1889,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1916,22 +1916,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Portfolio Risk ManagerPortfolio Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Portfolio-Risk-Manager-018983/1411339000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Business Resilience - Third Party Risk ManagementBusiness Resilience - Third Party Risk ManagementCorporate StrategySingapore, SG, 018983BCM</t>
+          <t>Associate, Principal IT Risk &amp; Control (IWM)Associate, Principal IT Risk &amp; Control (IWM)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Business-Resilience-Third-Party-Risk-Management-018983/1411348500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Principal-IT-Risk-&amp;-Control-%28IWM%29-018983/1411331000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1430,22 +1430,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1484,22 +1484,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,22 +1511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,22 +1538,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1889,22 +1889,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
